--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingTemplate.xlsx
@@ -62,6 +62,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -152,6 +159,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingTemplate.xlsx
@@ -32,6 +32,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,6 +54,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -84,6 +98,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -99,6 +120,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -114,6 +142,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -129,6 +164,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -144,6 +186,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -836,10 +885,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1161,13 +1210,13 @@
     <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" customWidth="1"/>
-    <col min="7" max="7" width="16.125" customWidth="1"/>
-    <col min="8" max="8" width="17.375" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingTemplate.xlsx
@@ -1216,7 +1216,7 @@
     <col min="9" max="9" width="17" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" ht="14.25" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1246,12 +1246,8 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1"/>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
-      <formula1>0</formula1>
-      <formula2>100000</formula2>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"月,周"</formula1>
     </dataValidation>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingTemplate.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsCfgSailingTemplate.xlsx
@@ -1246,14 +1246,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>"月,周"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I$1:I$1048576">
-      <formula1>32874</formula1>
-      <formula2>73050</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
